--- a/doc/crosspos/2d-cross-pos-taxonomy.xlsx
+++ b/doc/crosspos/2d-cross-pos-taxonomy.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="889">
   <si>
     <t>synset</t>
   </si>
@@ -426,7 +426,7 @@
     <t>{rejse_1§1}</t>
   </si>
   <si>
-    <t>{rejse_2§1e} &lt;https://wordnet.dk/dannet/data/synset-63836&gt;; {rejse_2§3} &lt;https://wordnet.dk/dannet/data/synset-31390&gt;; {rejse_2§2b} &lt;https://wordnet.dk/dannet/data/synset-70201&gt;</t>
+    <t>{rejse_3§1a} &lt;https://wordnet.dk/dannet/data/synset-33326&gt;; {rejse_2§1e} &lt;https://wordnet.dk/dannet/data/synset-63836&gt;; {rejse_2§3} &lt;https://wordnet.dk/dannet/data/synset-31390&gt;; {rejse_3§1b} &lt;https://wordnet.dk/dannet/data/synset-30765&gt;; {rejse_2§1g} &lt;https://wordnet.dk/dannet/data/synset-44925&gt;; {rejse_2§1d} &lt;https://wordnet.dk/dannet/data/synset-27582&gt;; {rejse_2§2c} &lt;https://wordnet.dk/dannet/data/synset-70974&gt;; {opstille_§1; rejse_2§1} &lt;https://wordnet.dk/dannet/data/synset-43268&gt;; {rejse_2§2b} &lt;https://wordnet.dk/dannet/data/synset-70201&gt;; {rejse_3§1} &lt;https://wordnet.dk/dannet/data/synset-14004&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-23260</t>
@@ -558,6 +558,15 @@
     <t>{fjerne_§1}</t>
   </si>
   <si>
+    <t>{fjernelse_§1} &lt;https://wordnet.dk/dannet/data/synset-27704&gt;</t>
+  </si>
+  <si>
+    <t>https://wordnet.dk/dannet/data/synset-27704</t>
+  </si>
+  <si>
+    <t>Automatisk forslag: hypernymets verbum som afledt substantiv.</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-27667</t>
   </si>
   <si>
@@ -657,6 +666,9 @@
     <t>https://wordnet.dk/dannet/data/synset-47653</t>
   </si>
   <si>
+    <t>Automatisk forslag: samme lemma som hypernymet, med synsettets ordklasse.</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-16490</t>
   </si>
   <si>
@@ -723,6 +735,9 @@
     <t>{skrive_§1}</t>
   </si>
   <si>
+    <t>{skrivelse_§1} &lt;https://wordnet.dk/dannet/data/synset-31800&gt;; {skrivning_§1} &lt;https://wordnet.dk/dannet/data/synset-30548&gt;; {skrivning_§2} &lt;https://wordnet.dk/dannet/data/synset-22583&gt;; {skriveri_§1} &lt;https://wordnet.dk/dannet/data/synset-7861&gt;; {skriveri_§2} &lt;https://wordnet.dk/dannet/data/synset-22568&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-22519</t>
   </si>
   <si>
@@ -762,6 +777,9 @@
     <t>{skriveri_§2}</t>
   </si>
   <si>
+    <t>{skrivelse_§1} &lt;https://wordnet.dk/dannet/data/synset-31800&gt;; {skrivning_§1} &lt;https://wordnet.dk/dannet/data/synset-30548&gt;; {skrivning_§2} &lt;https://wordnet.dk/dannet/data/synset-22583&gt;; {skriveri_§1} &lt;https://wordnet.dk/dannet/data/synset-7861&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-22568</t>
   </si>
   <si>
@@ -783,6 +801,9 @@
     <t>{frembringe_§1}</t>
   </si>
   <si>
+    <t>{frembringelse_§1} &lt;https://wordnet.dk/dannet/data/synset-23835&gt;; {frembringelse_§2} &lt;https://wordnet.dk/dannet/data/synset-23836&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-30440</t>
   </si>
   <si>
@@ -915,6 +936,9 @@
     <t>{erklære_§1}</t>
   </si>
   <si>
+    <t>{erklæring_§2} &lt;https://wordnet.dk/dannet/data/synset-34875&gt;; {erklæring_§1; udtalelse_§1} &lt;https://wordnet.dk/dannet/data/synset-31812&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-30655</t>
   </si>
   <si>
@@ -987,6 +1011,9 @@
     <t>{fremstille_§1}</t>
   </si>
   <si>
+    <t>{fremstilling_§2} &lt;https://wordnet.dk/dannet/data/synset-41329&gt;; {fremstilling_§2a} &lt;https://wordnet.dk/dannet/data/synset-7844&gt;; {fremstilling_§1} &lt;https://wordnet.dk/dannet/data/synset-30453&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-31914</t>
   </si>
   <si>
@@ -1050,6 +1077,9 @@
     <t>{skrivning_§2}</t>
   </si>
   <si>
+    <t>{skrivelse_§1} &lt;https://wordnet.dk/dannet/data/synset-31800&gt;; {skrivning_§1} &lt;https://wordnet.dk/dannet/data/synset-30548&gt;; {skriveri_§1} &lt;https://wordnet.dk/dannet/data/synset-7861&gt;; {skriveri_§2} &lt;https://wordnet.dk/dannet/data/synset-22568&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-22583</t>
   </si>
   <si>
@@ -1059,6 +1089,9 @@
     <t>{anbringe_§1}</t>
   </si>
   <si>
+    <t>{anbringelse_§1} &lt;https://wordnet.dk/dannet/data/synset-75200&gt;; {anbringelse_§1a} &lt;https://wordnet.dk/dannet/data/synset-72671&gt;; {anbringelse_§2} &lt;https://wordnet.dk/dannet/data/synset-75186&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-27523</t>
   </si>
   <si>
@@ -1185,6 +1218,9 @@
     <t>{meddele_§1}</t>
   </si>
   <si>
+    <t>{meddelelse_§1} &lt;https://wordnet.dk/dannet/data/synset-31791&gt;; {meddelelse_§1a} &lt;https://wordnet.dk/dannet/data/synset-75273&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-30794</t>
   </si>
   <si>
@@ -1245,6 +1281,12 @@
     <t>{opstå_§1}</t>
   </si>
   <si>
+    <t>{opståen_§1} &lt;https://wordnet.dk/dannet/data/synset-75282&gt;</t>
+  </si>
+  <si>
+    <t>https://wordnet.dk/dannet/data/synset-75282</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-55043</t>
   </si>
   <si>
@@ -1329,6 +1371,9 @@
     <t>{berette_§1; fortælle_§2}</t>
   </si>
   <si>
+    <t>{fortælling_§1} &lt;https://wordnet.dk/dannet/data/synset-37721&gt;; {fortælling_§2} &lt;https://wordnet.dk/dannet/data/synset-72742&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-72735</t>
   </si>
   <si>
@@ -1338,6 +1383,12 @@
     <t>{fortælling_§2}</t>
   </si>
   <si>
+    <t>{fortælling_§1} &lt;https://wordnet.dk/dannet/data/synset-37721&gt;</t>
+  </si>
+  <si>
+    <t>https://wordnet.dk/dannet/data/synset-37721</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-72742</t>
   </si>
   <si>
@@ -1401,7 +1452,7 @@
     <t>{hvile_1§1}</t>
   </si>
   <si>
-    <t>{hvile_2§2(1)} &lt;https://wordnet.dk/dannet/data/synset-66760&gt;; {hvile_2§2(3)} &lt;https://wordnet.dk/dannet/data/synset-77839&gt;; {hvile_2§2(2)} &lt;https://wordnet.dk/dannet/data/synset-77838&gt;</t>
+    <t>{hvile_2§1} &lt;https://wordnet.dk/dannet/data/synset-48812&gt;; {hvile_2§2(3)} &lt;https://wordnet.dk/dannet/data/synset-77839&gt;; {hvile_2§2(1)} &lt;https://wordnet.dk/dannet/data/synset-66760&gt;; {hvile_2§2a} &lt;https://wordnet.dk/dannet/data/synset-47331&gt;; {hvile_2§2(2)} &lt;https://wordnet.dk/dannet/data/synset-77838&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-70804</t>
@@ -1428,7 +1479,7 @@
     <t>{slå_2§1}</t>
   </si>
   <si>
-    <t>{slå_1§1} &lt;https://wordnet.dk/dannet/data/synset-34111&gt;</t>
+    <t>{slå_1§1} &lt;https://wordnet.dk/dannet/data/synset-34111&gt;; {slåning_§1} &lt;https://wordnet.dk/dannet/data/synset-28203&gt;; {slåen_§1} &lt;https://wordnet.dk/dannet/data/synset-1365&gt;; {slåen_§1a; slåenbær_§1} &lt;https://wordnet.dk/dannet/data/synset-26991&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-34111</t>
@@ -1449,6 +1500,9 @@
     <t>{slåning_§1}</t>
   </si>
   <si>
+    <t>{slå_1§1} &lt;https://wordnet.dk/dannet/data/synset-34111&gt;; {slåen_§1} &lt;https://wordnet.dk/dannet/data/synset-1365&gt;; {slåen_§1a; slåenbær_§1} &lt;https://wordnet.dk/dannet/data/synset-26991&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-28203</t>
   </si>
   <si>
@@ -1518,6 +1572,9 @@
     <t>{betale_§1}</t>
   </si>
   <si>
+    <t>{betaling_§1} &lt;https://wordnet.dk/dannet/data/synset-47482&gt;; {betaling_§2} &lt;https://wordnet.dk/dannet/data/synset-8425&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-53721</t>
   </si>
   <si>
@@ -1575,7 +1632,7 @@
     <t>{tale_1§1}</t>
   </si>
   <si>
-    <t>{tale_2§1} &lt;https://wordnet.dk/dannet/data/synset-30583&gt;; {tale_2§3a} &lt;https://wordnet.dk/dannet/data/synset-48443&gt;; {tale_2§3} &lt;https://wordnet.dk/dannet/data/synset-288&gt;</t>
+    <t>{tale_2§1a} &lt;https://wordnet.dk/dannet/data/synset-21990&gt;; {tale_2§1} &lt;https://wordnet.dk/dannet/data/synset-30583&gt;; {tale_2§1e} &lt;https://wordnet.dk/dannet/data/synset-30584&gt;; {tale_2§3b} &lt;https://wordnet.dk/dannet/data/synset-32125&gt;; {tale_2§4a} &lt;https://wordnet.dk/dannet/data/synset-31050&gt;; {tale_2§3} &lt;https://wordnet.dk/dannet/data/synset-288&gt;; {tale_2§5} &lt;https://wordnet.dk/dannet/data/synset-31049&gt;; {tale_2§1b} &lt;https://wordnet.dk/dannet/data/synset-48424&gt;; {tale_2§3a} &lt;https://wordnet.dk/dannet/data/synset-48443&gt;; {tale_2§4} &lt;https://wordnet.dk/dannet/data/synset-48358&gt;; {tale_2§1d} &lt;https://wordnet.dk/dannet/data/synset-21991&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-48291</t>
@@ -1596,6 +1653,9 @@
     <t>{undersøge_§1}</t>
   </si>
   <si>
+    <t>{opinionsmåling_§1; opinionsundersøgelse_§1; undersøgelse_§2a} &lt;https://wordnet.dk/dannet/data/synset-27331&gt;; {undersøgelse_§1b} &lt;https://wordnet.dk/dannet/data/synset-27391&gt;; {undersøgelse_§1a} &lt;https://wordnet.dk/dannet/data/synset-27390&gt;; {undersøgelse_§2} &lt;https://wordnet.dk/dannet/data/synset-64346&gt;; {undersøgelse_§1} &lt;https://wordnet.dk/dannet/data/synset-27358&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-41692</t>
   </si>
   <si>
@@ -1635,6 +1695,9 @@
     <t>{divergens_§1}</t>
   </si>
   <si>
+    <t>{afvigelse_§2} &lt;https://wordnet.dk/dannet/data/synset-27667&gt;; {afvigelse_§1a} &lt;https://wordnet.dk/dannet/data/synset-49204&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-72341</t>
   </si>
   <si>
@@ -1644,6 +1707,12 @@
     <t>{anlægge_§1}</t>
   </si>
   <si>
+    <t>{anlæggelse_§1} &lt;https://wordnet.dk/dannet/data/synset-28341&gt;</t>
+  </si>
+  <si>
+    <t>https://wordnet.dk/dannet/data/synset-28341</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-73134</t>
   </si>
   <si>
@@ -1656,6 +1725,12 @@
     <t>{bebygge_§1}</t>
   </si>
   <si>
+    <t>{bebyggelse_§1; byggeri_§2} &lt;https://wordnet.dk/dannet/data/synset-4761&gt;</t>
+  </si>
+  <si>
+    <t>https://wordnet.dk/dannet/data/synset-4761</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-55139</t>
   </si>
   <si>
@@ -1680,6 +1755,9 @@
     <t>{beskytte_§1}</t>
   </si>
   <si>
+    <t>{beskyttelse_§1} &lt;https://wordnet.dk/dannet/data/synset-2708&gt;; {beskyttelse_§1a} &lt;https://wordnet.dk/dannet/data/synset-22970&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-70153</t>
   </si>
   <si>
@@ -1776,6 +1854,9 @@
     <t>{forandre_§1; lave_2§11 om; ændre_§1}</t>
   </si>
   <si>
+    <t>{forandring_§1; ændring_§1} &lt;https://wordnet.dk/dannet/data/synset-33957&gt;; {celleforandring_§1; forandring_§1b} &lt;https://wordnet.dk/dannet/data/synset-33894&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-61432</t>
   </si>
   <si>
@@ -1800,6 +1881,9 @@
     <t>{forene_§1}</t>
   </si>
   <si>
+    <t>{forening_§1(1); klub_§1b} &lt;https://wordnet.dk/dannet/data/synset-17014&gt;; {forening_§2} &lt;https://wordnet.dk/dannet/data/synset-66779&gt;; {forening_§1(2)} &lt;https://wordnet.dk/dannet/data/synset-48023&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-64358</t>
   </si>
   <si>
@@ -1812,6 +1896,9 @@
     <t>{forhøje_§2}</t>
   </si>
   <si>
+    <t>{forhøjelse_§1a} &lt;https://wordnet.dk/dannet/data/synset-45271&gt;; {forhøjelse_§2} &lt;https://wordnet.dk/dannet/data/synset-57922&gt;; {forhøjning_§1} &lt;https://wordnet.dk/dannet/data/synset-7164&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-57933</t>
   </si>
   <si>
@@ -1824,6 +1911,12 @@
     <t>{forlade_§3a}</t>
   </si>
   <si>
+    <t>{forladelse_§1} &lt;https://wordnet.dk/dannet/data/synset-72542&gt;</t>
+  </si>
+  <si>
+    <t>https://wordnet.dk/dannet/data/synset-72542</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-69520</t>
   </si>
   <si>
@@ -1836,6 +1929,9 @@
     <t>{forsyne_§1}</t>
   </si>
   <si>
+    <t>{forsyning_§2} &lt;https://wordnet.dk/dannet/data/synset-67932&gt;; {forsyning_§1} &lt;https://wordnet.dk/dannet/data/synset-49116&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-72471</t>
   </si>
   <si>
@@ -1893,6 +1989,9 @@
     <t>{gøre_§1; handle_§1}</t>
   </si>
   <si>
+    <t>{ceremoni_§1; handling_§1a} &lt;https://wordnet.dk/dannet/data/synset-25329&gt;; {handling_§2} &lt;https://wordnet.dk/dannet/data/synset-72587&gt;; {handling_§1} &lt;https://wordnet.dk/dannet/data/synset-11677&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-2331</t>
   </si>
   <si>
@@ -1938,7 +2037,7 @@
     <t>{hvid_2§1a}</t>
   </si>
   <si>
-    <t>{hvid_1§1} &lt;https://wordnet.dk/dannet/data/synset-74694&gt;; {hvid_1§1a} &lt;https://wordnet.dk/dannet/data/synset-18020&gt;</t>
+    <t>{hvid_1§1a} &lt;https://wordnet.dk/dannet/data/synset-18020&gt;; {hvid_1§1} &lt;https://wordnet.dk/dannet/data/synset-74694&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-14898</t>
@@ -1989,6 +2088,9 @@
     <t>{indtage_§1; røre_2§1c}</t>
   </si>
   <si>
+    <t>{indtag_§1; indtagelse_§1; indtagning_§2} &lt;https://wordnet.dk/dannet/data/synset-41024&gt;; {rørelse_§1} &lt;https://wordnet.dk/dannet/data/synset-14727&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-74000</t>
   </si>
   <si>
@@ -2049,7 +2151,7 @@
     <t>{klage_1§2}</t>
   </si>
   <si>
-    <t>{klage_2§1} &lt;https://wordnet.dk/dannet/data/synset-32127&gt;; {klage_2§2} &lt;https://wordnet.dk/dannet/data/synset-68096&gt;; {klage_2§1a} &lt;https://wordnet.dk/dannet/data/synset-21903&gt;</t>
+    <t>{klage_2§1a} &lt;https://wordnet.dk/dannet/data/synset-21903&gt;; {klage_2§1} &lt;https://wordnet.dk/dannet/data/synset-32127&gt;; {klage_2§2} &lt;https://wordnet.dk/dannet/data/synset-68096&gt;; {klage_2§2a} &lt;https://wordnet.dk/dannet/data/synset-73700&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-49070</t>
@@ -2064,6 +2166,12 @@
     <t>{krænke_§1}</t>
   </si>
   <si>
+    <t>{krænkelse_§1a} &lt;https://wordnet.dk/dannet/data/synset-7905&gt;</t>
+  </si>
+  <si>
+    <t>https://wordnet.dk/dannet/data/synset-7905</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-69808</t>
   </si>
   <si>
@@ -2076,6 +2184,9 @@
     <t>{lave_2§12 til; lave_2§1a; præparere_§1; tilberede_§1; tillave_§1}</t>
   </si>
   <si>
+    <t>{lavning_§1} &lt;https://wordnet.dk/dannet/data/synset-18320&gt;; {tilberedning_§1} &lt;https://wordnet.dk/dannet/data/synset-31973&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-31946</t>
   </si>
   <si>
@@ -2088,7 +2199,7 @@
     <t>{le_2§1}</t>
   </si>
   <si>
-    <t>{le_1§1} &lt;https://wordnet.dk/dannet/data/synset-1957&gt;</t>
+    <t>{le_1§1} &lt;https://wordnet.dk/dannet/data/synset-1957&gt;; {len_§1a} &lt;https://wordnet.dk/dannet/data/synset-7620&gt;; {len_§1} &lt;https://wordnet.dk/dannet/data/synset-18102&gt;; {len_§2} &lt;https://wordnet.dk/dannet/data/synset-18103&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-1957</t>
@@ -2109,6 +2220,9 @@
     <t>{lege_§1; legende_2§1}</t>
   </si>
   <si>
+    <t>{legende_1§2} &lt;https://wordnet.dk/dannet/data/synset-5870&gt;; {legende_1§1a} &lt;https://wordnet.dk/dannet/data/synset-37051&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-49304</t>
   </si>
   <si>
@@ -2325,7 +2439,7 @@
     <t>{tiltale_1§2}</t>
   </si>
   <si>
-    <t>{tiltale_2§2} &lt;https://wordnet.dk/dannet/data/synset-73553&gt;; {tiltale_2§3} &lt;https://wordnet.dk/dannet/data/synset-32132&gt;; {tiltale_2§3a} &lt;https://wordnet.dk/dannet/data/synset-73882&gt;</t>
+    <t>{tiltale_2§3} &lt;https://wordnet.dk/dannet/data/synset-32132&gt;; {tiltale_2§3a} &lt;https://wordnet.dk/dannet/data/synset-73882&gt;; {tiltale_2§2} &lt;https://wordnet.dk/dannet/data/synset-73553&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-73870</t>
@@ -2364,6 +2478,9 @@
     <t>{udnytte_§1}</t>
   </si>
   <si>
+    <t>{udnyttelse_§2} &lt;https://wordnet.dk/dannet/data/synset-48512&gt;; {udnyttelse_§1} &lt;https://wordnet.dk/dannet/data/synset-69795&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-73965</t>
   </si>
   <si>
@@ -2376,6 +2493,9 @@
     <t>{udvikle_§1}</t>
   </si>
   <si>
+    <t>{udvikling_§1a} &lt;https://wordnet.dk/dannet/data/synset-77986&gt;; {udvikling_§2} &lt;https://wordnet.dk/dannet/data/synset-37094&gt;; {udvikling_§3} &lt;https://wordnet.dk/dannet/data/synset-57710&gt;; {udvikling_§1} &lt;https://wordnet.dk/dannet/data/synset-37065&gt;</t>
+  </si>
+  <si>
     <t>https://wordnet.dk/dannet/data/synset-53235</t>
   </si>
   <si>
@@ -2388,7 +2508,7 @@
     <t>{varme_2§1}</t>
   </si>
   <si>
-    <t>{varme_1§5} &lt;https://wordnet.dk/dannet/data/synset-72640&gt;; {varme_1§3} &lt;https://wordnet.dk/dannet/data/synset-47391&gt;; {varme_1§3a} &lt;https://wordnet.dk/dannet/data/synset-45361&gt;</t>
+    <t>{varme_1§4} &lt;https://wordnet.dk/dannet/data/synset-14327&gt;; {varme_1§3} &lt;https://wordnet.dk/dannet/data/synset-47391&gt;; {varme_1§3a} &lt;https://wordnet.dk/dannet/data/synset-45361&gt;; {varme_1§2} &lt;https://wordnet.dk/dannet/data/synset-25669&gt;; {varme_1§3b} &lt;https://wordnet.dk/dannet/data/synset-57238&gt;; {varme_1§5} &lt;https://wordnet.dk/dannet/data/synset-72640&gt;; {varme_1§1} &lt;https://wordnet.dk/dannet/data/synset-57300&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-72486</t>
@@ -2413,6 +2533,9 @@
   </si>
   <si>
     <t>{vokse_1§1}</t>
+  </si>
+  <si>
+    <t>{voksen_1§1} &lt;https://wordnet.dk/dannet/data/synset-5479&gt;; {voksen_1§1a} &lt;https://wordnet.dk/dannet/data/synset-3632&gt;</t>
   </si>
   <si>
     <t>https://wordnet.dk/dannet/data/synset-30604</t>
@@ -5503,10 +5626,10 @@
         <v>14.0</v>
       </c>
       <c r="E82" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>14</v>
@@ -5515,18 +5638,18 @@
         <v>14</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J82" t="s" s="0">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K82" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="1">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B83" t="s" s="0">
         <v>179</v>
@@ -5538,10 +5661,10 @@
         <v>14.0</v>
       </c>
       <c r="E83" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>14</v>
@@ -5550,18 +5673,18 @@
         <v>14</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J83" t="s" s="0">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K83" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="1">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>179</v>
@@ -5573,10 +5696,10 @@
         <v>14.0</v>
       </c>
       <c r="E84" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>14</v>
@@ -5585,18 +5708,18 @@
         <v>14</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J84" t="s" s="0">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K84" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="1">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B85" t="s" s="0">
         <v>179</v>
@@ -5608,10 +5731,10 @@
         <v>14.0</v>
       </c>
       <c r="E85" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>14</v>
@@ -5620,18 +5743,18 @@
         <v>14</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J85" t="s" s="0">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K85" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="1">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>179</v>
@@ -5643,10 +5766,10 @@
         <v>14.0</v>
       </c>
       <c r="E86" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>14</v>
@@ -5655,18 +5778,18 @@
         <v>14</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J86" t="s" s="0">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K86" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="1">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B87" t="s" s="0">
         <v>179</v>
@@ -5678,10 +5801,10 @@
         <v>14.0</v>
       </c>
       <c r="E87" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>14</v>
@@ -5690,18 +5813,18 @@
         <v>14</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J87" t="s" s="0">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K87" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="1">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B88" t="s" s="0">
         <v>179</v>
@@ -5713,10 +5836,10 @@
         <v>14.0</v>
       </c>
       <c r="E88" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>14</v>
@@ -5725,18 +5848,18 @@
         <v>14</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J88" t="s" s="0">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K88" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="1">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B89" t="s" s="0">
         <v>179</v>
@@ -5748,10 +5871,10 @@
         <v>14.0</v>
       </c>
       <c r="E89" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F89" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>14</v>
@@ -5760,18 +5883,18 @@
         <v>14</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J89" t="s" s="0">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K89" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="1">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B90" t="s" s="0">
         <v>179</v>
@@ -5783,10 +5906,10 @@
         <v>14.0</v>
       </c>
       <c r="E90" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F90" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>14</v>
@@ -5795,18 +5918,18 @@
         <v>14</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J90" t="s" s="0">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K90" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="1">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B91" t="s" s="0">
         <v>179</v>
@@ -5818,10 +5941,10 @@
         <v>14.0</v>
       </c>
       <c r="E91" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>14</v>
@@ -5830,18 +5953,18 @@
         <v>14</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J91" t="s" s="0">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K91" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="1">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B92" t="s" s="0">
         <v>179</v>
@@ -5853,10 +5976,10 @@
         <v>14.0</v>
       </c>
       <c r="E92" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F92" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>14</v>
@@ -5865,18 +5988,18 @@
         <v>14</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J92" t="s" s="0">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K92" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="1">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B93" t="s" s="0">
         <v>179</v>
@@ -5888,10 +6011,10 @@
         <v>14.0</v>
       </c>
       <c r="E93" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>14</v>
@@ -5900,18 +6023,18 @@
         <v>14</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J93" t="s" s="0">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K93" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="1">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B94" t="s" s="0">
         <v>179</v>
@@ -5923,10 +6046,10 @@
         <v>14.0</v>
       </c>
       <c r="E94" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F94" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>14</v>
@@ -5935,18 +6058,18 @@
         <v>14</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J94" t="s" s="0">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K94" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="1">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B95" t="s" s="0">
         <v>179</v>
@@ -5958,10 +6081,10 @@
         <v>14.0</v>
       </c>
       <c r="E95" t="s" s="0">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>14</v>
@@ -5970,33 +6093,33 @@
         <v>14</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J95" t="s" s="0">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K95" t="s" s="0">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="1">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B96" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C96" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D96" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E96" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>14</v>
@@ -6005,33 +6128,33 @@
         <v>14</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J96" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K96" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="1">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B97" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C97" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D97" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E97" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>14</v>
@@ -6040,33 +6163,33 @@
         <v>14</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J97" t="s" s="0">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="1">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C98" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D98" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E98" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>14</v>
@@ -6075,33 +6198,33 @@
         <v>14</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J98" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="K98" t="s" s="0">
         <v>219</v>
-      </c>
-      <c r="K98" t="s" s="0">
-        <v>215</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="1">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B99" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C99" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D99" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E99" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>14</v>
@@ -6110,33 +6233,33 @@
         <v>14</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J99" t="s" s="0">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="1">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D100" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E100" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>14</v>
@@ -6145,33 +6268,33 @@
         <v>14</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J100" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="1">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B101" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C101" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D101" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E101" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>14</v>
@@ -6180,33 +6303,33 @@
         <v>14</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J101" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="1">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C102" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D102" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E102" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>14</v>
@@ -6215,33 +6338,33 @@
         <v>14</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J102" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="1">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C103" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D103" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E103" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>14</v>
@@ -6250,33 +6373,33 @@
         <v>14</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J103" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="1">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C104" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D104" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>14</v>
@@ -6285,33 +6408,33 @@
         <v>14</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J104" t="s" s="0">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="1">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B105" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C105" t="s" s="1">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D105" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="E105" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>14</v>
@@ -6320,30 +6443,30 @@
         <v>14</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J105" t="s" s="0">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K105" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="1">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B106" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C106" t="s" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D106" t="n" s="0">
         <v>9.0</v>
       </c>
       <c r="E106" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>14</v>
@@ -6358,27 +6481,27 @@
         <v>14</v>
       </c>
       <c r="J106" t="s" s="0">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K106" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="1">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B107" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C107" t="s" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D107" t="n" s="0">
         <v>9.0</v>
       </c>
       <c r="E107" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>14</v>
@@ -6393,27 +6516,27 @@
         <v>14</v>
       </c>
       <c r="J107" t="s" s="0">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K107" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="1">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B108" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C108" t="s" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D108" t="n" s="0">
         <v>9.0</v>
       </c>
       <c r="E108" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F108" t="s" s="2">
         <v>14</v>
@@ -6428,27 +6551,27 @@
         <v>14</v>
       </c>
       <c r="J108" t="s" s="0">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K108" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="1">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B109" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C109" t="s" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D109" t="n" s="0">
         <v>9.0</v>
       </c>
       <c r="E109" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F109" t="s" s="2">
         <v>14</v>
@@ -6463,27 +6586,27 @@
         <v>14</v>
       </c>
       <c r="J109" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K109" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="1">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B110" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C110" t="s" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D110" t="n" s="0">
         <v>9.0</v>
       </c>
       <c r="E110" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F110" t="s" s="2">
         <v>14</v>
@@ -6498,27 +6621,27 @@
         <v>14</v>
       </c>
       <c r="J110" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K110" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="1">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B111" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C111" t="s" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D111" t="n" s="0">
         <v>9.0</v>
       </c>
       <c r="E111" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F111" t="s" s="2">
         <v>14</v>
@@ -6533,27 +6656,27 @@
         <v>14</v>
       </c>
       <c r="J111" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K111" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="1">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B112" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C112" t="s" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D112" t="n" s="0">
         <v>9.0</v>
       </c>
       <c r="E112" t="s" s="0">
-        <v>14</v>
+        <v>254</v>
       </c>
       <c r="F112" t="s" s="2">
         <v>14</v>
@@ -6568,27 +6691,27 @@
         <v>14</v>
       </c>
       <c r="J112" t="s" s="0">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="K112" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="1">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B113" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C113" t="s" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D113" t="n" s="0">
         <v>9.0</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F113" t="s" s="2">
         <v>14</v>
@@ -6603,27 +6726,27 @@
         <v>14</v>
       </c>
       <c r="J113" t="s" s="0">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="K113" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="1">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B114" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C114" t="s" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D114" t="n" s="0">
         <v>9.0</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F114" t="s" s="2">
         <v>14</v>
@@ -6638,27 +6761,27 @@
         <v>14</v>
       </c>
       <c r="J114" t="s" s="0">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="K114" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="1">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B115" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C115" t="s" s="1">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D115" t="n" s="0">
         <v>7.0</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="F115" t="s" s="2">
         <v>14</v>
@@ -6673,27 +6796,27 @@
         <v>14</v>
       </c>
       <c r="J115" t="s" s="0">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="K115" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="1">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B116" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C116" t="s" s="1">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D116" t="n" s="0">
         <v>7.0</v>
       </c>
       <c r="E116" t="s" s="0">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="F116" t="s" s="2">
         <v>14</v>
@@ -6708,27 +6831,27 @@
         <v>14</v>
       </c>
       <c r="J116" t="s" s="0">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="K116" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="1">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B117" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C117" t="s" s="1">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D117" t="n" s="0">
         <v>7.0</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="F117" t="s" s="2">
         <v>14</v>
@@ -6743,27 +6866,27 @@
         <v>14</v>
       </c>
       <c r="J117" t="s" s="0">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="K117" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="1">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B118" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C118" t="s" s="1">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D118" t="n" s="0">
         <v>7.0</v>
       </c>
       <c r="E118" t="s" s="0">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="F118" t="s" s="2">
         <v>14</v>
@@ -6778,27 +6901,27 @@
         <v>14</v>
       </c>
       <c r="J118" t="s" s="0">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="K118" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="1">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B119" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C119" t="s" s="1">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D119" t="n" s="0">
         <v>7.0</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="F119" t="s" s="2">
         <v>14</v>
@@ -6813,27 +6936,27 @@
         <v>14</v>
       </c>
       <c r="J119" t="s" s="0">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="K119" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="1">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B120" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C120" t="s" s="1">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D120" t="n" s="0">
         <v>7.0</v>
       </c>
       <c r="E120" t="s" s="0">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="F120" t="s" s="2">
         <v>14</v>
@@ -6848,27 +6971,27 @@
         <v>14</v>
       </c>
       <c r="J120" t="s" s="0">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K120" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="1">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B121" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C121" t="s" s="1">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D121" t="n" s="0">
         <v>7.0</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="F121" t="s" s="2">
         <v>14</v>
@@ -6883,30 +7006,30 @@
         <v>14</v>
       </c>
       <c r="J121" t="s" s="0">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="K121" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="1">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B122" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C122" t="s" s="1">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D122" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="E122" t="s" s="0">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F122" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>14</v>
@@ -6915,33 +7038,33 @@
         <v>14</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J122" t="s" s="0">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="K122" t="s" s="0">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="1">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B123" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C123" t="s" s="1">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D123" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F123" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>14</v>
@@ -6950,33 +7073,33 @@
         <v>14</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J123" t="s" s="0">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K123" t="s" s="0">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="1">
+        <v>285</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C124" t="s" s="1">
         <v>278</v>
-      </c>
-      <c r="B124" t="s" s="0">
-        <v>210</v>
-      </c>
-      <c r="C124" t="s" s="1">
-        <v>271</v>
       </c>
       <c r="D124" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="E124" t="s" s="0">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F124" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>14</v>
@@ -6985,33 +7108,33 @@
         <v>14</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J124" t="s" s="0">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K124" t="s" s="0">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="1">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B125" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C125" t="s" s="1">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D125" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="E125" t="s" s="0">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F125" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>14</v>
@@ -7020,33 +7143,33 @@
         <v>14</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J125" t="s" s="0">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="K125" t="s" s="0">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="1">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B126" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C126" t="s" s="1">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D126" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="E126" t="s" s="0">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F126" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>14</v>
@@ -7055,33 +7178,33 @@
         <v>14</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J126" t="s" s="0">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="K126" t="s" s="0">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="1">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B127" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C127" t="s" s="1">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D127" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="E127" t="s" s="0">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F127" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>14</v>
@@ -7090,24 +7213,24 @@
         <v>14</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J127" t="s" s="0">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="K127" t="s" s="0">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="1">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B128" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C128" t="s" s="1">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D128" t="n" s="0">
         <v>5.0</v>
@@ -7128,21 +7251,21 @@
         <v>14</v>
       </c>
       <c r="J128" t="s" s="0">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="K128" t="s" s="0">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="1">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B129" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C129" t="s" s="1">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D129" t="n" s="0">
         <v>5.0</v>
@@ -7163,21 +7286,21 @@
         <v>14</v>
       </c>
       <c r="J129" t="s" s="0">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="K129" t="s" s="0">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="1">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B130" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C130" t="s" s="1">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D130" t="n" s="0">
         <v>5.0</v>
@@ -7198,21 +7321,21 @@
         <v>14</v>
       </c>
       <c r="J130" t="s" s="0">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="K130" t="s" s="0">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="1">
+        <v>301</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C131" t="s" s="1">
         <v>294</v>
-      </c>
-      <c r="B131" t="s" s="0">
-        <v>210</v>
-      </c>
-      <c r="C131" t="s" s="1">
-        <v>287</v>
       </c>
       <c r="D131" t="n" s="0">
         <v>5.0</v>
@@ -7233,21 +7356,21 @@
         <v>14</v>
       </c>
       <c r="J131" t="s" s="0">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="K131" t="s" s="0">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="1">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B132" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C132" t="s" s="1">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D132" t="n" s="0">
         <v>5.0</v>
@@ -7268,27 +7391,27 @@
         <v>14</v>
       </c>
       <c r="J132" t="s" s="0">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="K132" t="s" s="0">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="1">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B133" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C133" t="s" s="1">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D133" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E133" t="s" s="0">
-        <v>14</v>
+        <v>307</v>
       </c>
       <c r="F133" t="s" s="2">
         <v>14</v>
@@ -7303,27 +7426,27 @@
         <v>14</v>
       </c>
       <c r="J133" t="s" s="0">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="K133" t="s" s="0">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="1">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B134" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C134" t="s" s="1">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D134" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E134" t="s" s="0">
-        <v>14</v>
+        <v>307</v>
       </c>
       <c r="F134" t="s" s="2">
         <v>14</v>
@@ -7338,27 +7461,27 @@
         <v>14</v>
       </c>
       <c r="J134" t="s" s="0">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="K134" t="s" s="0">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="1">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B135" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C135" t="s" s="1">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D135" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E135" t="s" s="0">
-        <v>14</v>
+        <v>307</v>
       </c>
       <c r="F135" t="s" s="2">
         <v>14</v>
@@ -7373,27 +7496,27 @@
         <v>14</v>
       </c>
       <c r="J135" t="s" s="0">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="K135" t="s" s="0">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="1">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B136" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C136" t="s" s="1">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D136" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E136" t="s" s="0">
-        <v>14</v>
+        <v>307</v>
       </c>
       <c r="F136" t="s" s="2">
         <v>14</v>
@@ -7408,27 +7531,27 @@
         <v>14</v>
       </c>
       <c r="J136" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="K136" t="s" s="0">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="1">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B137" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C137" t="s" s="1">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D137" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E137" t="s" s="0">
-        <v>14</v>
+        <v>307</v>
       </c>
       <c r="F137" t="s" s="2">
         <v>14</v>
@@ -7443,21 +7566,21 @@
         <v>14</v>
       </c>
       <c r="J137" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="K137" t="s" s="0">
         <v>309</v>
-      </c>
-      <c r="K137" t="s" s="0">
-        <v>301</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="1">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B138" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C138" t="s" s="1">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D138" t="n" s="0">
         <v>5.0</v>
@@ -7478,21 +7601,21 @@
         <v>14</v>
       </c>
       <c r="J138" t="s" s="0">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="K138" t="s" s="0">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="1">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B139" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C139" t="s" s="1">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D139" t="n" s="0">
         <v>5.0</v>
@@ -7513,21 +7636,21 @@
         <v>14</v>
       </c>
       <c r="J139" t="s" s="0">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="K139" t="s" s="0">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="1">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B140" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C140" t="s" s="1">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D140" t="n" s="0">
         <v>5.0</v>
@@ -7548,21 +7671,21 @@
         <v>14</v>
       </c>
       <c r="J140" t="s" s="0">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="K140" t="s" s="0">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="1">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B141" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C141" t="s" s="1">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D141" t="n" s="0">
         <v>5.0</v>
@@ -7583,21 +7706,21 @@
         <v>14</v>
       </c>
       <c r="J141" t="s" s="0">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="K141" t="s" s="0">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="1">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B142" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C142" t="s" s="1">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D142" t="n" s="0">
         <v>5.0</v>
@@ -7618,27 +7741,27 @@
         <v>14</v>
       </c>
       <c r="J142" t="s" s="0">
+        <v>329</v>
+      </c>
+      <c r="K142" t="s" s="0">
         <v>321</v>
-      </c>
-      <c r="K142" t="s" s="0">
-        <v>313</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="1">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B143" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C143" t="s" s="1">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D143" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E143" t="s" s="0">
-        <v>14</v>
+        <v>332</v>
       </c>
       <c r="F143" t="s" s="2">
         <v>14</v>
@@ -7653,27 +7776,27 @@
         <v>14</v>
       </c>
       <c r="J143" t="s" s="0">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="K143" t="s" s="0">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="1">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B144" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C144" t="s" s="1">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D144" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E144" t="s" s="0">
-        <v>14</v>
+        <v>332</v>
       </c>
       <c r="F144" t="s" s="2">
         <v>14</v>
@@ -7688,27 +7811,27 @@
         <v>14</v>
       </c>
       <c r="J144" t="s" s="0">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="K144" t="s" s="0">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="1">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B145" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C145" t="s" s="1">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D145" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E145" t="s" s="0">
-        <v>14</v>
+        <v>332</v>
       </c>
       <c r="F145" t="s" s="2">
         <v>14</v>
@@ -7723,27 +7846,27 @@
         <v>14</v>
       </c>
       <c r="J145" t="s" s="0">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="K145" t="s" s="0">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="1">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B146" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C146" t="s" s="1">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D146" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E146" t="s" s="0">
-        <v>14</v>
+        <v>332</v>
       </c>
       <c r="F146" t="s" s="2">
         <v>14</v>
@@ -7758,27 +7881,27 @@
         <v>14</v>
       </c>
       <c r="J146" t="s" s="0">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="K146" t="s" s="0">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="1">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B147" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C147" t="s" s="1">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D147" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E147" t="s" s="0">
-        <v>14</v>
+        <v>332</v>
       </c>
       <c r="F147" t="s" s="2">
         <v>14</v>
@@ -7793,27 +7916,27 @@
         <v>14</v>
       </c>
       <c r="J147" t="s" s="0">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="K147" t="s" s="0">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="1">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B148" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C148" t="s" s="1">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D148" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E148" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F148" t="s" s="2">
         <v>14</v>
@@ -7828,27 +7951,27 @@
         <v>14</v>
       </c>
       <c r="J148" t="s" s="0">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="K148" t="s" s="0">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="1">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B149" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C149" t="s" s="1">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D149" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E149" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F149" t="s" s="2">
         <v>14</v>
@@ -7863,27 +7986,27 @@
         <v>14</v>
       </c>
       <c r="J149" t="s" s="0">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="K149" t="s" s="0">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="1">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B150" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C150" t="s" s="1">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D150" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E150" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F150" t="s" s="2">
         <v>14</v>
@@ -7898,27 +8021,27 @@
         <v>14</v>
       </c>
       <c r="J150" t="s" s="0">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="K150" t="s" s="0">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="1">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B151" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C151" t="s" s="1">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D151" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E151" t="s" s="0">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F151" t="s" s="2">
         <v>14</v>
@@ -7933,27 +8056,27 @@
         <v>14</v>
       </c>
       <c r="J151" t="s" s="0">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="K151" t="s" s="0">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="1">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B152" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C152" t="s" s="1">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D152" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="E152" t="s" s="0">
-        <v>14</v>
+        <v>354</v>
       </c>
       <c r="F152" t="s" s="2">
         <v>14</v>
@@ -7968,27 +8091,27 @@
         <v>14</v>
       </c>
       <c r="J152" t="s" s="0">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="K152" t="s" s="0">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="1">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B153" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C153" t="s" s="1">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="D153" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E153" t="s" s="0">
-        <v>14</v>
+        <v>358</v>
       </c>
       <c r="F153" t="s" s="2">
         <v>14</v>
@@ -8003,27 +8126,27 @@
         <v>14</v>
       </c>
       <c r="J153" t="s" s="0">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="K153" t="s" s="0">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="1">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B154" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C154" t="s" s="1">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="D154" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E154" t="s" s="0">
-        <v>14</v>
+        <v>358</v>
       </c>
       <c r="F154" t="s" s="2">
         <v>14</v>
@@ -8038,27 +8161,27 @@
         <v>14</v>
       </c>
       <c r="J154" t="s" s="0">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="K154" t="s" s="0">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="1">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B155" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C155" t="s" s="1">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="D155" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E155" t="s" s="0">
-        <v>14</v>
+        <v>358</v>
       </c>
       <c r="F155" t="s" s="2">
         <v>14</v>
@@ -8073,27 +8196,27 @@
         <v>14</v>
       </c>
       <c r="J155" t="s" s="0">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="K155" t="s" s="0">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="1">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B156" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C156" t="s" s="1">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="D156" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E156" t="s" s="0">
-        <v>14</v>
+        <v>358</v>
       </c>
       <c r="F156" t="s" s="2">
         <v>14</v>
@@ -8108,21 +8231,21 @@
         <v>14</v>
       </c>
       <c r="J156" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="K156" t="s" s="0">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="1">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B157" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C157" t="s" s="1">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="D157" t="n" s="0">
         <v>4.0</v>
@@ -8143,21 +8266,21 @@
         <v>14</v>
       </c>
       <c r="J157" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="K157" t="s" s="0">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="1">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B158" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C158" t="s" s="1">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="D158" t="n" s="0">
         <v>4.0</v>
@@ -8178,21 +8301,21 @@
         <v>14</v>
       </c>
       <c r="J158" t="s" s="0">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="K158" t="s" s="0">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="1">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="B159" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C159" t="s" s="1">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="D159" t="n" s="0">
         <v>4.0</v>
@@ -8213,21 +8336,21 @@
         <v>14</v>
       </c>
       <c r="J159" t="s" s="0">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="K159" t="s" s="0">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="1">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B160" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C160" t="s" s="1">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="D160" t="n" s="0">
         <v>4.0</v>
@@ -8248,21 +8371,21 @@
         <v>14</v>
       </c>
       <c r="J160" t="s" s="0">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="K160" t="s" s="0">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="1">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B161" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C161" t="s" s="1">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D161" t="n" s="0">
         <v>4.0</v>
@@ -8283,21 +8406,21 @@
         <v>14</v>
       </c>
       <c r="J161" t="s" s="0">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="K161" t="s" s="0">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="1">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B162" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C162" t="s" s="1">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D162" t="n" s="0">
         <v>4.0</v>
@@ -8318,21 +8441,21 @@
         <v>14</v>
       </c>
       <c r="J162" t="s" s="0">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="K162" t="s" s="0">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="1">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B163" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C163" t="s" s="1">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D163" t="n" s="0">
         <v>4.0</v>
@@ -8353,21 +8476,21 @@
         <v>14</v>
       </c>
       <c r="J163" t="s" s="0">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="K163" t="s" s="0">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="1">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B164" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C164" t="s" s="1">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D164" t="n" s="0">
         <v>4.0</v>
@@ -8388,30 +8511,30 @@
         <v>14</v>
       </c>
       <c r="J164" t="s" s="0">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="K164" t="s" s="0">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="1">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B165" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C165" t="s" s="1">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D165" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E165" t="s" s="0">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F165" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="G165" t="s" s="2">
         <v>14</v>
@@ -8420,33 +8543,33 @@
         <v>14</v>
       </c>
       <c r="I165" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J165" t="s" s="0">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="K165" t="s" s="0">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="1">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B166" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C166" t="s" s="1">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D166" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E166" t="s" s="0">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F166" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="G166" t="s" s="2">
         <v>14</v>
@@ -8455,33 +8578,33 @@
         <v>14</v>
       </c>
       <c r="I166" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J166" t="s" s="0">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="K166" t="s" s="0">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="1">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B167" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C167" t="s" s="1">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D167" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E167" t="s" s="0">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F167" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="G167" t="s" s="2">
         <v>14</v>
@@ -8490,33 +8613,33 @@
         <v>14</v>
       </c>
       <c r="I167" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J167" t="s" s="0">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="K167" t="s" s="0">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="1">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B168" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C168" t="s" s="1">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D168" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E168" t="s" s="0">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F168" t="s" s="2">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="G168" t="s" s="2">
         <v>14</v>
@@ -8525,30 +8648,30 @@
         <v>14</v>
       </c>
       <c r="I168" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J168" t="s" s="0">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="K168" t="s" s="0">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="1">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B169" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C169" t="s" s="1">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D169" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E169" t="s" s="0">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F169" t="s" s="2">
         <v>14</v>
@@ -8563,27 +8686,27 @@
         <v>14</v>
       </c>
       <c r="J169" t="s" s="0">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="K169" t="s" s="0">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="1">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B170" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C170" t="s" s="1">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D170" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E170" t="s" s="0">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F170" t="s" s="2">
         <v>14</v>
@@ -8598,27 +8721,27 @@
         <v>14</v>
       </c>
       <c r="J170" t="s" s="0">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="K170" t="s" s="0">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="1">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B171" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C171" t="s" s="1">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D171" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E171" t="s" s="0">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F171" t="s" s="2">
         <v>14</v>
@@ -8633,27 +8756,27 @@
         <v>14</v>
       </c>
       <c r="J171" t="s" s="0">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="K171" t="s" s="0">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="1">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B172" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C172" t="s" s="1">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D172" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E172" t="s" s="0">
-        <v>14</v>
+        <v>401</v>
       </c>
       <c r="F172" t="s" s="2">
         <v>14</v>
@@ -8668,21 +8791,21 @@
         <v>14</v>
       </c>
       <c r="J172" t="s" s="0">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="K172" t="s" s="0">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="1">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B173" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C173" t="s" s="1">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D173" t="n" s="0">
         <v>4.0</v>
@@ -8703,21 +8826,21 @@
         <v>14</v>
       </c>
       <c r="J173" t="s" s="0">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="K173" t="s" s="0">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="1">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B174" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C174" t="s" s="1">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D174" t="n" s="0">
         <v>4.0</v>
@@ -8738,21 +8861,21 @@
         <v>14</v>
       </c>
       <c r="J174" t="s" s="0">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="K174" t="s" s="0">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="1">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B175" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C175" t="s" s="1">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D175" t="n" s="0">
         <v>4.0</v>
@@ -8773,21 +8896,21 @@
         <v>14</v>
       </c>
       <c r="J175" t="s" s="0">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="K175" t="s" s="0">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="1">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B176" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C176" t="s" s="1">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D176" t="n" s="0">
         <v>4.0</v>
@@ -8808,30 +8931,30 @@
         <v>14</v>
       </c>
       <c r="J176" t="s" s="0">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="K176" t="s" s="0">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="1">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B177" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C177" t="s" s="1">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="D177" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E177" t="s" s="0">
-        <v>14</v>
+        <v>422</v>
       </c>
       <c r="F177" t="s" s="2">
-        <v>14</v>
+        <v>423</v>
       </c>
       <c r="G177" t="s" s="2">
         <v>14</v>
@@ -8840,33 +8963,33 @@
         <v>14</v>
       </c>
       <c r="I177" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J177" t="s" s="0">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="K177" t="s" s="0">
-        <v>411</v>
+        <v>425</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="1">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="B178" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C178" t="s" s="1">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="D178" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E178" t="s" s="0">
-        <v>14</v>
+        <v>422</v>
       </c>
       <c r="F178" t="s" s="2">
-        <v>14</v>
+        <v>423</v>
       </c>
       <c r="G178" t="s" s="2">
         <v>14</v>
@@ -8875,33 +8998,33 @@
         <v>14</v>
       </c>
       <c r="I178" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J178" t="s" s="0">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="K178" t="s" s="0">
-        <v>411</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="1">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="B179" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C179" t="s" s="1">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="D179" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E179" t="s" s="0">
-        <v>14</v>
+        <v>422</v>
       </c>
       <c r="F179" t="s" s="2">
-        <v>14</v>
+        <v>423</v>
       </c>
       <c r="G179" t="s" s="2">
         <v>14</v>
@@ -8910,33 +9033,33 @@
         <v>14</v>
       </c>
       <c r="I179" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J179" t="s" s="0">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="K179" t="s" s="0">
-        <v>411</v>
+        <v>425</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="1">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="B180" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C180" t="s" s="1">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="D180" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="E180" t="s" s="0">
-        <v>14</v>
+        <v>422</v>
       </c>
       <c r="F180" t="s" s="2">
-        <v>14</v>
+        <v>423</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>14</v>
@@ -8945,33 +9068,33 @@
         <v>14</v>
       </c>
       <c r="I180" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J180" t="s" s="0">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="K180" t="s" s="0">
-        <v>411</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="1">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B181" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C181" t="s" s="1">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="D181" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E181" t="s" s="0">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="F181" t="s" s="2">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="G181" t="s" s="2">
         <v>14</v>
@@ -8980,33 +9103,33 @@
         <v>14</v>
       </c>
       <c r="I181" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J181" t="s" s="0">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="K181" t="s" s="0">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="1">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="B182" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C182" t="s" s="1">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="D182" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E182" t="s" s="0">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="F182" t="s" s="2">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="G182" t="s" s="2">
         <v>14</v>
@@ -9015,33 +9138,33 @@
         <v>14</v>
       </c>
       <c r="I182" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J182" t="s" s="0">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="K182" t="s" s="0">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="1">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="B183" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C183" t="s" s="1">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="D183" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E183" t="s" s="0">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="F183" t="s" s="2">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>14</v>
@@ -9050,33 +9173,33 @@
         <v>14</v>
       </c>
       <c r="I183" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J183" t="s" s="0">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="K183" t="s" s="0">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="1">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="B184" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C184" t="s" s="1">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="D184" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E184" t="s" s="0">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="F184" t="s" s="2">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="G184" t="s" s="2">
         <v>14</v>
@@ -9085,33 +9208,33 @@
         <v>14</v>
       </c>
       <c r="I184" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J184" t="s" s="0">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="K184" t="s" s="0">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="1">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="B185" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C185" t="s" s="1">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="D185" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E185" t="s" s="0">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="F185" t="s" s="2">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="G185" t="s" s="2">
         <v>14</v>
@@ -9120,33 +9243,33 @@
         <v>14</v>
       </c>
       <c r="I185" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J185" t="s" s="0">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="K185" t="s" s="0">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="1">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B186" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C186" t="s" s="1">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="D186" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E186" t="s" s="0">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="F186" t="s" s="2">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="G186" t="s" s="2">
         <v>14</v>
@@ -9155,30 +9278,30 @@
         <v>14</v>
       </c>
       <c r="I186" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J186" t="s" s="0">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="K186" t="s" s="0">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="1">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="B187" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C187" t="s" s="1">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="D187" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E187" t="s" s="0">
-        <v>14</v>
+        <v>452</v>
       </c>
       <c r="F187" t="s" s="2">
         <v>14</v>
@@ -9193,30 +9316,30 @@
         <v>14</v>
       </c>
       <c r="J187" t="s" s="0">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="K187" t="s" s="0">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="1">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="B188" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C188" t="s" s="1">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="D188" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E188" t="s" s="0">
-        <v>14</v>
+        <v>456</v>
       </c>
       <c r="F188" t="s" s="2">
-        <v>14</v>
+        <v>457</v>
       </c>
       <c r="G188" t="s" s="2">
         <v>14</v>
@@ -9225,30 +9348,30 @@
         <v>14</v>
       </c>
       <c r="I188" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J188" t="s" s="0">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="K188" t="s" s="0">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="1">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="B189" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C189" t="s" s="1">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="D189" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E189" t="s" s="0">
-        <v>14</v>
+        <v>452</v>
       </c>
       <c r="F189" t="s" s="2">
         <v>14</v>
@@ -9263,21 +9386,21 @@
         <v>14</v>
       </c>
       <c r="J189" t="s" s="0">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="K189" t="s" s="0">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="1">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B190" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C190" t="s" s="1">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="D190" t="n" s="0">
         <v>3.0</v>
@@ -9298,21 +9421,21 @@
         <v>14</v>
       </c>
       <c r="J190" t="s" s="0">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="K190" t="s" s="0">
-        <v>447</v>
+        <v>464</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="1">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="B191" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C191" t="s" s="1">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="D191" t="n" s="0">
         <v>3.0</v>
@@ -9333,21 +9456,21 @@
         <v>14</v>
       </c>
       <c r="J191" t="s" s="0">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="K191" t="s" s="0">
-        <v>447</v>
+        <v>464</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="1">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="B192" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C192" t="s" s="1">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="D192" t="n" s="0">
         <v>3.0</v>
@@ -9368,21 +9491,21 @@
         <v>14</v>
       </c>
       <c r="J192" t="s" s="0">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="K192" t="s" s="0">
-        <v>447</v>
+        <v>464</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="1">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="B193" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C193" t="s" s="1">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="D193" t="n" s="0">
         <v>3.0</v>
@@ -9403,21 +9526,21 @@
         <v>14</v>
       </c>
       <c r="J193" t="s" s="0">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="K193" t="s" s="0">
-        <v>455</v>
+        <v>472</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="1">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="B194" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C194" t="s" s="1">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="D194" t="n" s="0">
         <v>3.0</v>
@@ -9438,21 +9561,21 @@
         <v>14</v>
       </c>
       <c r="J194" t="s" s="0">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="K194" t="s" s="0">
-        <v>455</v>
+        <v>472</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="1">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="B195" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C195" t="s" s="1">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="D195" t="n" s="0">
         <v>3.0</v>
@@ -9473,27 +9596,27 @@
         <v>14</v>
       </c>
       <c r="J195" t="s" s="0">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="K195" t="s" s="0">
-        <v>455</v>
+        <v>472</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="1">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="B196" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C196" t="s" s="1">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="D196" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E196" t="s" s="0">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="F196" t="s" s="2">
         <v>14</v>
@@ -9508,27 +9631,27 @@
         <v>14</v>
       </c>
       <c r="J196" t="s" s="0">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="K196" t="s" s="0">
-        <v>464</v>
+        <v>481</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="1">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="B197" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C197" t="s" s="1">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="D197" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E197" t="s" s="0">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="F197" t="s" s="2">
         <v>14</v>
@@ -9543,27 +9666,27 @@
         <v>14</v>
       </c>
       <c r="J197" t="s" s="0">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="K197" t="s" s="0">
-        <v>464</v>
+        <v>481</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="1">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="B198" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C198" t="s" s="1">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="D198" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E198" t="s" s="0">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="F198" t="s" s="2">
         <v>14</v>
@@ -9578,30 +9701,30 @@
         <v>14</v>
       </c>
       <c r="J198" t="s" s="0">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="K198" t="s" s="0">
-        <v>464</v>
+        <v>481</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="1">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="B199" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C199" t="s" s="1">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="D199" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E199" t="s" s="0">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="F199" t="s" s="2">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="G199" t="s" s="2">
         <v>14</v>
@@ -9613,30 +9736,30 @@
         <v>14</v>
       </c>
       <c r="J199" t="s" s="0">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="K199" t="s" s="0">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="1">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="B200" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C200" t="s" s="1">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="D200" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E200" t="s" s="0">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="F200" t="s" s="2">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="G200" t="s" s="2">
         <v>14</v>
@@ -9648,30 +9771,30 @@
         <v>14</v>
       </c>
       <c r="J200" t="s" s="0">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="K200" t="s" s="0">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="1">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="B201" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C201" t="s" s="1">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="D201" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="E201" t="s" s="0">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="F201" t="s" s="2">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="G201" t="s" s="2">
         <v>14</v>
@@ -9683,21 +9806,21 @@
         <v>14</v>
       </c>
       <c r="J201" t="s" s="0">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="K201" t="s" s="0">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="1">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B202" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C202" t="s" s="1">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="D202" t="n" s="0">
         <v>3.0</v>
@@ -9718,21 +9841,21 @@
         <v>14</v>
       </c>
       <c r="J202" t="s" s="0">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="K202" t="s" s="0">
-        <v>482</v>
+        <v>500</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="1">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="B203" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C203" t="s" s="1">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="D203" t="n" s="0">
         <v>3.0</v>
@@ -9753,21 +9876,21 @@
         <v>14</v>
       </c>
       <c r="J203" t="s" s="0">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="K203" t="s" s="0">
-        <v>482</v>
+        <v>500</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s" s="1">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="B204" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C204" t="s" s="1">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="D204" t="n" s="0">
         <v>3.0</v>
@@ -9788,21 +9911,21 @@
         <v>14</v>
       </c>
       <c r="J204" t="s" s="0">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="K204" t="s" s="0">
-        <v>482</v>
+        <v>500</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="1">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="B205" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C205" t="s" s="1">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="D205" t="n" s="0">
         <v>2.0</v>
@@ -9823,21 +9946,21 @@
         <v>14</v>
       </c>
       <c r="J205" t="s" s="0">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="K205" t="s" s="0">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="1">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="B206" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C206" t="s" s="1">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="D206" t="n" s="0">
         <v>2.0</v>
@@ -9858,21 +9981,21 @@
         <v>14</v>
       </c>
       <c r="J206" t="s" s="0">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="K206" t="s" s="0">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="1">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B207" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C207" t="s" s="1">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D207" t="n" s="0">
         <v>2.0</v>
@@ -9893,21 +10016,21 @@
         <v>14</v>
       </c>
       <c r="J207" t="s" s="0">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="K207" t="s" s="0">
-        <v>495</v>
+        <v>513</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="1">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="B208" t="s" s="0">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="C208" t="s" s="1">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D208" t="n" s="0">
         <v>2.0</v>
@@ -9928,27 +10051,27 @@
         <v>14</v>
       </c>
       <c r="J208" t="s" s="0">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="K208" t="s" s="0">
-        <v>495</v>
+        <v>513</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="1">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="B209" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C209" t="s" s="1">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="D209" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E209" t="s" s="0">
-        <v>14</v>
+        <v>519</v>
       </c>
       <c r="F209" t="s" s="2">
         <v>14</v>
@@ -9963,27 +10086,27 @@
         <v>14</v>
       </c>
       <c r="J209" t="s" s="0">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="K209" t="s" s="0">
-        <v>502</v>
+        <v>521</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="1">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="B210" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C210" t="s" s="1">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="D210" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E210" t="s" s="0">
-        <v>14</v>
+        <v>519</v>
       </c>
       <c r="F210" t="s" s="2">
         <v>14</v>
@@ -9998,30 +10121,30 @@
         <v>14</v>
       </c>
       <c r="J210" t="s" s="0">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="K210" t="s" s="0">
-        <v>502</v>
+        <v>521</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="1">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="B211" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C211" t="s" s="1">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="D211" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E211" t="s" s="0">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="F211" t="s" s="2">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="G211" t="s" s="2">
         <v>14</v>
@@ -10030,33 +10153,33 @@
         <v>14</v>
       </c>
       <c r="I211" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J211" t="s" s="0">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="K211" t="s" s="0">
-        <v>509</v>
+        <v>528</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="1">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="B212" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C212" t="s" s="1">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="D212" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E212" t="s" s="0">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="F212" t="s" s="2">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="G212" t="s" s="2">
         <v>14</v>
@@ -10065,24 +10188,24 @@
         <v>14</v>
       </c>
       <c r="I212" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="J212" t="s" s="0">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="K212" t="s" s="0">
-        <v>509</v>
+        <v>528</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="1">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="B213" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C213" t="s" s="1">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="D213" t="n" s="0">
         <v>2.0</v>
@@ -10103,21 +10226,21 @@
         <v>14</v>
       </c>
       <c r="J213" t="s" s="0">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="K213" t="s" s="0">
-        <v>515</v>
+        <v>534</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="1">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="B214" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C214" t="s" s="1">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="D214" t="n" s="0">
         <v>2.0</v>
@@ -10138,27 +10261,27 @@
         <v>14</v>
       </c>
       <c r="J214" t="s" s="0">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K214" t="s" s="0">
-        <v>515</v>
+        <v>534</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s" s="1">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="B215" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C215" t="s" s="1">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="D215" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E215" t="s" s="0">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="F215" t="s" s="2">
         <v>14</v>
@@ -10173,27 +10296,27 @@
         <v>14</v>
       </c>
       <c r="J215" t="s" s="0">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="K215" t="s" s="0">
-        <v>522</v>
+        <v>541</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="1">
-        <v>523</v>
+        <v>542</v>
       </c>
       <c r="B216" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C216" t="s" s="1">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="D216" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E216" t="s" s="0">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="F216" t="s" s="2">
         <v>14</v>
@@ -10208,27 +10331,27 @@
         <v>14</v>
       </c>
       <c r="J216" t="s" s="0">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="K216" t="s" s="0">
-        <v>522</v>
+        <v>541</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="1">
-        <v>525</v>
+        <v>544</v>
       </c>
       <c r="B217" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C217" t="s" s="1">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="D217" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E217" t="s" s="0">
-        <v>14</v>
+        <v>546</v>
       </c>
       <c r="F217" t="s" s="2">
         <v>14</v>
@@ -10243,27 +10366,27 @@
         <v>14</v>
       </c>
       <c r="J217" t="s" s="0">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="K217" t="s" s="0">
-        <v>528</v>
+        <v>548</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="1">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="B218" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C218" t="s" s="1">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="D218" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="E218" t="s" s="0">
-        <v>14</v>
+        <v>546</v>
       </c>
       <c r="F218" t="s" s="2">
         <v>14</v>
@@ -10278,21 +10401,21 @@
         <v>14</v>
       </c>
       <c r="J218" t="s" s="0">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="K218" t="s" s="0">
-        <v>528</v>
+        <v>548</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s" s="1">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="B219" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C219" t="s" s="1">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="D219" t="n" s="0">
         <v>1.0</v>
@@ -10313,21 +10436,21 @@
         <v>14</v>
       </c>
       <c r="J219" t="s" s="0">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="K219" t="s" s="0">
-        <v>534</v>
+        <v>554</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s" s="1">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="B220" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C220" t="s" s="1">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="D220" t="n" s="0">
         <v>1.0</v>
@@ -10348,27 +10471,27 @@
         <v>14</v>
       </c>
       <c r="J220" t="s" s="0">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="K220" t="s" s="0">
-        <v>538</v>
+        <v>558</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s" s="1">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="B221" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C221" t="s" s="1">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D221" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E221" t="s" s="0">
-        <v>14</v>
+        <v>560</v>
       </c>
       <c r="F221" t="s" s="2">
         <v>14</v>
@@ -10383,30 +10506,30 @@
         <v>14</v>
       </c>
       <c r="J221" t="s" s="0">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="K221" t="s" s="0">
-        <v>368</v>
+        <v>379</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s" s="1">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="B222" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C222" t="s" s="1">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="D222" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E222" t="s" s="0">
-        <v>14</v>
+        <v>564</v>
       </c>
       <c r="F222" t="s" s="2">
-        <v>14</v>
+        <v>565</v>
       </c>
       <c r="G222" t="s" s="2">
         <v>14</v>
@@ -10415,33 +10538,33 @@
         <v>14</v>
       </c>
       <c r="I222" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J222" t="s" s="0">
-        <v>543</v>
+        <v>566</v>
       </c>
       <c r="K222" t="s" s="0">
-        <v>544</v>
+        <v>567</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="1">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="B223" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C223" t="s" s="1">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="D223" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E223" t="s" s="0">
-        <v>14</v>
+        <v>570</v>
       </c>
       <c r="F223" t="s" s="2">
-        <v>14</v>
+        <v>571</v>
       </c>
       <c r="G223" t="s" s="2">
         <v>14</v>
@@ -10450,24 +10573,24 @@
         <v>14</v>
       </c>
       <c r="I223" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J223" t="s" s="0">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="K223" t="s" s="0">
-        <v>548</v>
+        <v>573</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="1">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="B224" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C224" t="s" s="1">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="D224" t="n" s="0">
         <v>1.0</v>
@@ -10488,27 +10611,27 @@
         <v>14</v>
       </c>
       <c r="J224" t="s" s="0">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="K224" t="s" s="0">
-        <v>552</v>
+        <v>577</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="1">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="B225" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C225" t="s" s="1">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="D225" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E225" t="s" s="0">
-        <v>14</v>
+        <v>580</v>
       </c>
       <c r="F225" t="s" s="2">
         <v>14</v>
@@ -10523,21 +10646,21 @@
         <v>14</v>
       </c>
       <c r="J225" t="s" s="0">
-        <v>555</v>
+        <v>581</v>
       </c>
       <c r="K225" t="s" s="0">
-        <v>556</v>
+        <v>582</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s" s="1">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="B226" t="s" s="0">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="C226" t="s" s="1">
-        <v>559</v>
+        <v>585</v>
       </c>
       <c r="D226" t="n" s="0">
         <v>1.0</v>
@@ -10558,21 +10681,21 @@
         <v>14</v>
       </c>
       <c r="J226" t="s" s="0">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="K226" t="s" s="0">
-        <v>561</v>
+        <v>587</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s" s="1">
-        <v>562</v>
+        <v>588</v>
       </c>
       <c r="B227" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C227" t="s" s="1">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="D227" t="n" s="0">
         <v>1.0</v>
@@ -10593,27 +10716,27 @@
         <v>14</v>
       </c>
       <c r="J227" t="s" s="0">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="K227" t="s" s="0">
-        <v>565</v>
+        <v>591</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="1">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="B228" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C228" t="s" s="1">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="D228" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E228" t="s" s="0">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="F228" t="s" s="2">
         <v>14</v>
@@ -10628,21 +10751,21 @@
         <v>14</v>
       </c>
       <c r="J228" t="s" s="0">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="K228" t="s" s="0">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="1">
-        <v>569</v>
+        <v>595</v>
       </c>
       <c r="B229" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C229" t="s" s="1">
-        <v>570</v>
+        <v>596</v>
       </c>
       <c r="D229" t="n" s="0">
         <v>1.0</v>
@@ -10663,21 +10786,21 @@
         <v>14</v>
       </c>
       <c r="J229" t="s" s="0">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="K229" t="s" s="0">
-        <v>572</v>
+        <v>598</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s" s="1">
-        <v>573</v>
+        <v>599</v>
       </c>
       <c r="B230" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C230" t="s" s="1">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="D230" t="n" s="0">
         <v>1.0</v>
@@ -10698,21 +10821,21 @@
         <v>14</v>
       </c>
       <c r="J230" t="s" s="0">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="K230" t="s" s="0">
-        <v>576</v>
+        <v>602</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="1">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="B231" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C231" t="s" s="1">
-        <v>578</v>
+        <v>604</v>
       </c>
       <c r="D231" t="n" s="0">
         <v>1.0</v>
@@ -10733,21 +10856,21 @@
         <v>14</v>
       </c>
       <c r="J231" t="s" s="0">
-        <v>579</v>
+        <v>605</v>
       </c>
       <c r="K231" t="s" s="0">
-        <v>580</v>
+        <v>606</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="1">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="B232" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C232" t="s" s="1">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="D232" t="n" s="0">
         <v>1.0</v>
@@ -10768,27 +10891,27 @@
         <v>14</v>
       </c>
       <c r="J232" t="s" s="0">
-        <v>583</v>
+        <v>609</v>
       </c>
       <c r="K232" t="s" s="0">
-        <v>584</v>
+        <v>610</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="1">
-        <v>585</v>
+        <v>611</v>
       </c>
       <c r="B233" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C233" t="s" s="1">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="D233" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E233" t="s" s="0">
-        <v>14</v>
+        <v>613</v>
       </c>
       <c r="F233" t="s" s="2">
         <v>14</v>
@@ -10803,21 +10926,21 @@
         <v>14</v>
       </c>
       <c r="J233" t="s" s="0">
-        <v>587</v>
+        <v>614</v>
       </c>
       <c r="K233" t="s" s="0">
-        <v>588</v>
+        <v>615</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="1">
-        <v>589</v>
+        <v>616</v>
       </c>
       <c r="B234" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C234" t="s" s="1">
-        <v>590</v>
+        <v>617</v>
       </c>
       <c r="D234" t="n" s="0">
         <v>1.0</v>
@@ -10838,27 +10961,27 @@
         <v>14</v>
       </c>
       <c r="J234" t="s" s="0">
-        <v>591</v>
+        <v>618</v>
       </c>
       <c r="K234" t="s" s="0">
-        <v>592</v>
+        <v>619</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="1">
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="B235" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C235" t="s" s="1">
-        <v>594</v>
+        <v>621</v>
       </c>
       <c r="D235" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E235" t="s" s="0">
-        <v>14</v>
+        <v>622</v>
       </c>
       <c r="F235" t="s" s="2">
         <v>14</v>
@@ -10873,27 +10996,27 @@
         <v>14</v>
       </c>
       <c r="J235" t="s" s="0">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="K235" t="s" s="0">
-        <v>596</v>
+        <v>624</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="1">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="B236" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C236" t="s" s="1">
-        <v>598</v>
+        <v>626</v>
       </c>
       <c r="D236" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E236" t="s" s="0">
-        <v>14</v>
+        <v>627</v>
       </c>
       <c r="F236" t="s" s="2">
         <v>14</v>
@@ -10908,30 +11031,30 @@
         <v>14</v>
       </c>
       <c r="J236" t="s" s="0">
-        <v>599</v>
+        <v>628</v>
       </c>
       <c r="K236" t="s" s="0">
-        <v>600</v>
+        <v>629</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s" s="1">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="B237" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C237" t="s" s="1">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="D237" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E237" t="s" s="0">
-        <v>14</v>
+        <v>632</v>
       </c>
       <c r="F237" t="s" s="2">
-        <v>14</v>
+        <v>633</v>
       </c>
       <c r="G237" t="s" s="2">
         <v>14</v>
@@ -10940,30 +11063,30 @@
         <v>14</v>
       </c>
       <c r="I237" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J237" t="s" s="0">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="K237" t="s" s="0">
-        <v>604</v>
+        <v>635</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s" s="1">
-        <v>605</v>
+        <v>636</v>
       </c>
       <c r="B238" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C238" t="s" s="1">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="D238" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E238" t="s" s="0">
-        <v>14</v>
+        <v>638</v>
       </c>
       <c r="F238" t="s" s="2">
         <v>14</v>
@@ -10978,21 +11101,21 @@
         <v>14</v>
       </c>
       <c r="J238" t="s" s="0">
-        <v>607</v>
+        <v>639</v>
       </c>
       <c r="K238" t="s" s="0">
-        <v>608</v>
+        <v>640</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s" s="1">
-        <v>609</v>
+        <v>641</v>
       </c>
       <c r="B239" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C239" t="s" s="1">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="D239" t="n" s="0">
         <v>1.0</v>
@@ -11013,21 +11136,21 @@
         <v>14</v>
       </c>
       <c r="J239" t="s" s="0">
-        <v>611</v>
+        <v>643</v>
       </c>
       <c r="K239" t="s" s="0">
-        <v>612</v>
+        <v>644</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s" s="1">
-        <v>613</v>
+        <v>645</v>
       </c>
       <c r="B240" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C240" t="s" s="1">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="D240" t="n" s="0">
         <v>1.0</v>
@@ -11048,21 +11171,21 @@
         <v>14</v>
       </c>
       <c r="J240" t="s" s="0">
-        <v>615</v>
+        <v>647</v>
       </c>
       <c r="K240" t="s" s="0">
-        <v>616</v>
+        <v>648</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="1">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="B241" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C241" t="s" s="1">
-        <v>618</v>
+        <v>650</v>
       </c>
       <c r="D241" t="n" s="0">
         <v>1.0</v>
@@ -11083,21 +11206,21 @@
         <v>14</v>
       </c>
       <c r="J241" t="s" s="0">
-        <v>619</v>
+        <v>651</v>
       </c>
       <c r="K241" t="s" s="0">
-        <v>620</v>
+        <v>652</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="1">
-        <v>621</v>
+        <v>653</v>
       </c>
       <c r="B242" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C242" t="s" s="1">
-        <v>622</v>
+        <v>654</v>
       </c>
       <c r="D242" t="n" s="0">
         <v>1.0</v>
@@ -11118,27 +11241,27 @@
         <v>14</v>
       </c>
       <c r="J242" t="s" s="0">
-        <v>623</v>
+        <v>655</v>
       </c>
       <c r="K242" t="s" s="0">
-        <v>624</v>
+        <v>656</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="1">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="B243" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C243" t="s" s="1">
-        <v>625</v>
+        <v>657</v>
       </c>
       <c r="D243" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E243" t="s" s="0">
-        <v>14</v>
+        <v>658</v>
       </c>
       <c r="F243" t="s" s="2">
         <v>14</v>
@@ -11153,21 +11276,21 @@
         <v>14</v>
       </c>
       <c r="J243" t="s" s="0">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="K243" t="s" s="0">
-        <v>626</v>
+        <v>659</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="1">
-        <v>627</v>
+        <v>660</v>
       </c>
       <c r="B244" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C244" t="s" s="1">
-        <v>628</v>
+        <v>661</v>
       </c>
       <c r="D244" t="n" s="0">
         <v>1.0</v>
@@ -11188,21 +11311,21 @@
         <v>14</v>
       </c>
       <c r="J244" t="s" s="0">
-        <v>629</v>
+        <v>662</v>
       </c>
       <c r="K244" t="s" s="0">
-        <v>630</v>
+        <v>663</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="1">
-        <v>631</v>
+        <v>664</v>
       </c>
       <c r="B245" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C245" t="s" s="1">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="D245" t="n" s="0">
         <v>1.0</v>
@@ -11223,21 +11346,21 @@
         <v>14</v>
       </c>
       <c r="J245" t="s" s="0">
-        <v>633</v>
+        <v>666</v>
       </c>
       <c r="K245" t="s" s="0">
-        <v>634</v>
+        <v>667</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="1">
-        <v>635</v>
+        <v>668</v>
       </c>
       <c r="B246" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C246" t="s" s="1">
-        <v>636</v>
+        <v>669</v>
       </c>
       <c r="D246" t="n" s="0">
         <v>1.0</v>
@@ -11258,27 +11381,27 @@
         <v>14</v>
       </c>
       <c r="J246" t="s" s="0">
-        <v>637</v>
+        <v>670</v>
       </c>
       <c r="K246" t="s" s="0">
-        <v>638</v>
+        <v>671</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="1">
-        <v>639</v>
+        <v>672</v>
       </c>
       <c r="B247" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C247" t="s" s="1">
-        <v>640</v>
+        <v>673</v>
       </c>
       <c r="D247" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E247" t="s" s="0">
-        <v>641</v>
+        <v>674</v>
       </c>
       <c r="F247" t="s" s="2">
         <v>14</v>
@@ -11293,21 +11416,21 @@
         <v>14</v>
       </c>
       <c r="J247" t="s" s="0">
-        <v>642</v>
+        <v>675</v>
       </c>
       <c r="K247" t="s" s="0">
-        <v>643</v>
+        <v>676</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s" s="1">
-        <v>644</v>
+        <v>677</v>
       </c>
       <c r="B248" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C248" t="s" s="1">
-        <v>645</v>
+        <v>678</v>
       </c>
       <c r="D248" t="n" s="0">
         <v>1.0</v>
@@ -11328,21 +11451,21 @@
         <v>14</v>
       </c>
       <c r="J248" t="s" s="0">
-        <v>646</v>
+        <v>679</v>
       </c>
       <c r="K248" t="s" s="0">
-        <v>647</v>
+        <v>680</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s" s="1">
-        <v>648</v>
+        <v>681</v>
       </c>
       <c r="B249" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C249" t="s" s="1">
-        <v>649</v>
+        <v>682</v>
       </c>
       <c r="D249" t="n" s="0">
         <v>1.0</v>
@@ -11363,21 +11486,21 @@
         <v>14</v>
       </c>
       <c r="J249" t="s" s="0">
-        <v>650</v>
+        <v>683</v>
       </c>
       <c r="K249" t="s" s="0">
-        <v>651</v>
+        <v>684</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s" s="1">
-        <v>652</v>
+        <v>685</v>
       </c>
       <c r="B250" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C250" t="s" s="1">
-        <v>653</v>
+        <v>686</v>
       </c>
       <c r="D250" t="n" s="0">
         <v>1.0</v>
@@ -11398,27 +11521,27 @@
         <v>14</v>
       </c>
       <c r="J250" t="s" s="0">
-        <v>654</v>
+        <v>687</v>
       </c>
       <c r="K250" t="s" s="0">
-        <v>655</v>
+        <v>688</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s" s="1">
-        <v>656</v>
+        <v>689</v>
       </c>
       <c r="B251" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C251" t="s" s="1">
-        <v>657</v>
+        <v>690</v>
       </c>
       <c r="D251" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E251" t="s" s="0">
-        <v>14</v>
+        <v>691</v>
       </c>
       <c r="F251" t="s" s="2">
         <v>14</v>
@@ -11433,21 +11556,21 @@
         <v>14</v>
       </c>
       <c r="J251" t="s" s="0">
-        <v>658</v>
+        <v>692</v>
       </c>
       <c r="K251" t="s" s="0">
-        <v>659</v>
+        <v>693</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s" s="1">
-        <v>660</v>
+        <v>694</v>
       </c>
       <c r="B252" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C252" t="s" s="1">
-        <v>661</v>
+        <v>695</v>
       </c>
       <c r="D252" t="n" s="0">
         <v>1.0</v>
@@ -11468,21 +11591,21 @@
         <v>14</v>
       </c>
       <c r="J252" t="s" s="0">
-        <v>662</v>
+        <v>696</v>
       </c>
       <c r="K252" t="s" s="0">
-        <v>663</v>
+        <v>697</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s" s="1">
-        <v>664</v>
+        <v>698</v>
       </c>
       <c r="B253" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C253" t="s" s="1">
-        <v>665</v>
+        <v>699</v>
       </c>
       <c r="D253" t="n" s="0">
         <v>1.0</v>
@@ -11503,21 +11626,21 @@
         <v>14</v>
       </c>
       <c r="J253" t="s" s="0">
-        <v>666</v>
+        <v>700</v>
       </c>
       <c r="K253" t="s" s="0">
-        <v>667</v>
+        <v>701</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s" s="1">
-        <v>668</v>
+        <v>702</v>
       </c>
       <c r="B254" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C254" t="s" s="1">
-        <v>669</v>
+        <v>703</v>
       </c>
       <c r="D254" t="n" s="0">
         <v>1.0</v>
@@ -11538,21 +11661,21 @@
         <v>14</v>
       </c>
       <c r="J254" t="s" s="0">
-        <v>670</v>
+        <v>704</v>
       </c>
       <c r="K254" t="s" s="0">
-        <v>671</v>
+        <v>705</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s" s="1">
-        <v>672</v>
+        <v>706</v>
       </c>
       <c r="B255" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C255" t="s" s="1">
-        <v>673</v>
+        <v>707</v>
       </c>
       <c r="D255" t="n" s="0">
         <v>1.0</v>
@@ -11573,27 +11696,27 @@
         <v>14</v>
       </c>
       <c r="J255" t="s" s="0">
-        <v>674</v>
+        <v>708</v>
       </c>
       <c r="K255" t="s" s="0">
-        <v>675</v>
+        <v>709</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s" s="1">
-        <v>676</v>
+        <v>710</v>
       </c>
       <c r="B256" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C256" t="s" s="1">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="D256" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E256" t="s" s="0">
-        <v>678</v>
+        <v>712</v>
       </c>
       <c r="F256" t="s" s="2">
         <v>14</v>
@@ -11608,30 +11731,30 @@
         <v>14</v>
       </c>
       <c r="J256" t="s" s="0">
-        <v>679</v>
+        <v>713</v>
       </c>
       <c r="K256" t="s" s="0">
-        <v>680</v>
+        <v>714</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s" s="1">
-        <v>681</v>
+        <v>715</v>
       </c>
       <c r="B257" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C257" t="s" s="1">
-        <v>682</v>
+        <v>716</v>
       </c>
       <c r="D257" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E257" t="s" s="0">
-        <v>14</v>
+        <v>717</v>
       </c>
       <c r="F257" t="s" s="2">
-        <v>14</v>
+        <v>718</v>
       </c>
       <c r="G257" t="s" s="2">
         <v>14</v>
@@ -11640,30 +11763,30 @@
         <v>14</v>
       </c>
       <c r="I257" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="J257" t="s" s="0">
-        <v>683</v>
+        <v>719</v>
       </c>
       <c r="K257" t="s" s="0">
-        <v>684</v>
+        <v>720</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s" s="1">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="B258" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C258" t="s" s="1">
-        <v>686</v>
+        <v>722</v>
       </c>
       <c r="D258" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E258" t="s" s="0">
-        <v>14</v>
+        <v>723</v>
       </c>
       <c r="F258" t="s" s="2">
         <v>14</v>
@@ -11678,30 +11801,30 @@
         <v>14</v>
       </c>
       <c r="J258" t="s" s="0">
-        <v>687</v>
+        <v>724</v>
       </c>
       <c r="K258" t="s" s="0">
-        <v>688</v>
+        <v>725</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s" s="1">
-        <v>689</v>
+        <v>726</v>
       </c>
       <c r="B259" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C259" t="s" s="1">
-        <v>690</v>
+        <v>727</v>
       </c>
       <c r="D259" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E259" t="s" s="0">
-        <v>691</v>
+        <v>728</v>
       </c>
       <c r="F259" t="s" s="2">
-        <v>692</v>
+        <v>729</v>
       </c>
       <c r="G259" t="s" s="2">
         <v>14</v>
@@ -11713,27 +11836,27 @@
         <v>14</v>
       </c>
       <c r="J259" t="s" s="0">
-        <v>693</v>
+        <v>730</v>
       </c>
       <c r="K259" t="s" s="0">
-        <v>694</v>
+        <v>731</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s" s="1">
-        <v>695</v>
+        <v>732</v>
       </c>
       <c r="B260" t="s" s="0">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="C260" t="s" s="1">
-        <v>697</v>
+        <v>734</v>
       </c>
       <c r="D260" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E260" t="s" s="0">
-        <v>14</v>
+        <v>735</v>
       </c>
       <c r="F260" t="s" s="2">
         <v>14</v>
@@ -11748,21 +11871,21 @@
         <v>14</v>
       </c>
       <c r="J260" t="s" s="0">
-        <v>698</v>
+        <v>736</v>
       </c>
       <c r="K260" t="s" s="0">
-        <v>699</v>
+        <v>737</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s" s="1">
-        <v>700</v>
+        <v>738</v>
       </c>
       <c r="B261" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C261" t="s" s="1">
-        <v>701</v>
+        <v>739</v>
       </c>
       <c r="D261" t="n" s="0">
         <v>1.0</v>
@@ -11783,21 +11906,21 @@
         <v>14</v>
       </c>
       <c r="J261" t="s" s="0">
-        <v>702</v>
+        <v>740</v>
       </c>
       <c r="K261" t="s" s="0">
-        <v>703</v>
+        <v>741</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s" s="1">
-        <v>704</v>
+        <v>742</v>
       </c>
       <c r="B262" t="s" s="0">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="C262" t="s" s="1">
-        <v>705</v>
+        <v>743</v>
       </c>
       <c r="D262" t="n" s="0">
         <v>1.0</v>
@@ -11818,21 +11941,21 @@
         <v>14</v>
       </c>
       <c r="J262" t="s" s="0">
-        <v>706</v>
+        <v>744</v>
       </c>
       <c r="K262" t="s" s="0">
-        <v>707</v>
+        <v>745</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="1">
-        <v>708</v>
+        <v>746</v>
       </c>
       <c r="B263" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C263" t="s" s="1">
-        <v>709</v>
+        <v>747</v>
       </c>
       <c r="D263" t="n" s="0">
         <v>1.0</v>
@@ -11853,21 +11976,21 @@
         <v>14</v>
       </c>
       <c r="J263" t="s" s="0">
-        <v>710</v>
+        <v>748</v>
       </c>
       <c r="K263" t="s" s="0">
-        <v>711</v>
+        <v>749</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s" s="1">
-        <v>712</v>
+        <v>750</v>
       </c>
       <c r="B264" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C264" t="s" s="1">
-        <v>713</v>
+        <v>751</v>
       </c>
       <c r="D264" t="n" s="0">
         <v>1.0</v>
@@ -11888,21 +12011,21 @@
         <v>14</v>
       </c>
       <c r="J264" t="s" s="0">
-        <v>714</v>
+        <v>752</v>
       </c>
       <c r="K264" t="s" s="0">
-        <v>715</v>
+        <v>753</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s" s="1">
-        <v>716</v>
+        <v>754</v>
       </c>
       <c r="B265" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C265" t="s" s="1">
-        <v>717</v>
+        <v>755</v>
       </c>
       <c r="D265" t="n" s="0">
         <v>1.0</v>
@@ -11923,21 +12046,21 @@
         <v>14</v>
       </c>
       <c r="J265" t="s" s="0">
-        <v>718</v>
+        <v>756</v>
       </c>
       <c r="K265" t="s" s="0">
-        <v>719</v>
+        <v>757</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s" s="1">
-        <v>720</v>
+        <v>758</v>
       </c>
       <c r="B266" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C266" t="s" s="1">
-        <v>721</v>
+        <v>759</v>
       </c>
       <c r="D266" t="n" s="0">
         <v>1.0</v>
@@ -11958,21 +12081,21 @@
         <v>14</v>
       </c>
       <c r="J266" t="s" s="0">
-        <v>722</v>
+        <v>760</v>
       </c>
       <c r="K266" t="s" s="0">
-        <v>723</v>
+        <v>761</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s" s="1">
-        <v>724</v>
+        <v>762</v>
       </c>
       <c r="B267" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C267" t="s" s="1">
-        <v>725</v>
+        <v>763</v>
       </c>
       <c r="D267" t="n" s="0">
         <v>1.0</v>
@@ -11993,21 +12116,21 @@
         <v>14</v>
       </c>
       <c r="J267" t="s" s="0">
-        <v>726</v>
+        <v>764</v>
       </c>
       <c r="K267" t="s" s="0">
-        <v>727</v>
+        <v>765</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s" s="1">
-        <v>728</v>
+        <v>766</v>
       </c>
       <c r="B268" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C268" t="s" s="1">
-        <v>729</v>
+        <v>767</v>
       </c>
       <c r="D268" t="n" s="0">
         <v>1.0</v>
@@ -12028,21 +12151,21 @@
         <v>14</v>
       </c>
       <c r="J268" t="s" s="0">
-        <v>730</v>
+        <v>768</v>
       </c>
       <c r="K268" t="s" s="0">
-        <v>731</v>
+        <v>769</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s" s="1">
-        <v>732</v>
+        <v>770</v>
       </c>
       <c r="B269" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C269" t="s" s="1">
-        <v>733</v>
+        <v>771</v>
       </c>
       <c r="D269" t="n" s="0">
         <v>1.0</v>
@@ -12063,21 +12186,21 @@
         <v>14</v>
       </c>
       <c r="J269" t="s" s="0">
-        <v>734</v>
+        <v>772</v>
       </c>
       <c r="K269" t="s" s="0">
-        <v>735</v>
+        <v>773</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s" s="1">
-        <v>736</v>
+        <v>774</v>
       </c>
       <c r="B270" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C270" t="s" s="1">
-        <v>737</v>
+        <v>775</v>
       </c>
       <c r="D270" t="n" s="0">
         <v>1.0</v>
@@ -12098,21 +12221,21 @@
         <v>14</v>
       </c>
       <c r="J270" t="s" s="0">
-        <v>738</v>
+        <v>776</v>
       </c>
       <c r="K270" t="s" s="0">
-        <v>739</v>
+        <v>777</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s" s="1">
-        <v>740</v>
+        <v>778</v>
       </c>
       <c r="B271" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C271" t="s" s="1">
-        <v>741</v>
+        <v>779</v>
       </c>
       <c r="D271" t="n" s="0">
         <v>1.0</v>
@@ -12133,21 +12256,21 @@
         <v>14</v>
       </c>
       <c r="J271" t="s" s="0">
-        <v>742</v>
+        <v>780</v>
       </c>
       <c r="K271" t="s" s="0">
-        <v>743</v>
+        <v>781</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s" s="1">
-        <v>744</v>
+        <v>782</v>
       </c>
       <c r="B272" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C272" t="s" s="1">
-        <v>745</v>
+        <v>783</v>
       </c>
       <c r="D272" t="n" s="0">
         <v>1.0</v>
@@ -12168,21 +12291,21 @@
         <v>14</v>
       </c>
       <c r="J272" t="s" s="0">
-        <v>746</v>
+        <v>784</v>
       </c>
       <c r="K272" t="s" s="0">
-        <v>747</v>
+        <v>785</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s" s="1">
-        <v>748</v>
+        <v>786</v>
       </c>
       <c r="B273" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C273" t="s" s="1">
-        <v>749</v>
+        <v>787</v>
       </c>
       <c r="D273" t="n" s="0">
         <v>1.0</v>
@@ -12203,21 +12326,21 @@
         <v>14</v>
       </c>
       <c r="J273" t="s" s="0">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="K273" t="s" s="0">
-        <v>751</v>
+        <v>789</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s" s="1">
-        <v>752</v>
+        <v>790</v>
       </c>
       <c r="B274" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C274" t="s" s="1">
-        <v>753</v>
+        <v>791</v>
       </c>
       <c r="D274" t="n" s="0">
         <v>1.0</v>
@@ -12238,21 +12361,21 @@
         <v>14</v>
       </c>
       <c r="J274" t="s" s="0">
-        <v>754</v>
+        <v>792</v>
       </c>
       <c r="K274" t="s" s="0">
-        <v>755</v>
+        <v>793</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s" s="1">
-        <v>756</v>
+        <v>794</v>
       </c>
       <c r="B275" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C275" t="s" s="1">
-        <v>757</v>
+        <v>795</v>
       </c>
       <c r="D275" t="n" s="0">
         <v>1.0</v>
@@ -12273,21 +12396,21 @@
         <v>14</v>
       </c>
       <c r="J275" t="s" s="0">
-        <v>758</v>
+        <v>796</v>
       </c>
       <c r="K275" t="s" s="0">
-        <v>759</v>
+        <v>797</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s" s="1">
-        <v>760</v>
+        <v>798</v>
       </c>
       <c r="B276" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C276" t="s" s="1">
-        <v>761</v>
+        <v>799</v>
       </c>
       <c r="D276" t="n" s="0">
         <v>1.0</v>
@@ -12308,21 +12431,21 @@
         <v>14</v>
       </c>
       <c r="J276" t="s" s="0">
-        <v>762</v>
+        <v>800</v>
       </c>
       <c r="K276" t="s" s="0">
-        <v>763</v>
+        <v>801</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s" s="1">
-        <v>764</v>
+        <v>802</v>
       </c>
       <c r="B277" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C277" t="s" s="1">
-        <v>765</v>
+        <v>803</v>
       </c>
       <c r="D277" t="n" s="0">
         <v>1.0</v>
@@ -12343,27 +12466,27 @@
         <v>14</v>
       </c>
       <c r="J277" t="s" s="0">
-        <v>766</v>
+        <v>804</v>
       </c>
       <c r="K277" t="s" s="0">
-        <v>767</v>
+        <v>805</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s" s="1">
-        <v>768</v>
+        <v>806</v>
       </c>
       <c r="B278" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C278" t="s" s="1">
-        <v>769</v>
+        <v>807</v>
       </c>
       <c r="D278" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E278" t="s" s="0">
-        <v>770</v>
+        <v>808</v>
       </c>
       <c r="F278" t="s" s="2">
         <v>14</v>
@@ -12378,21 +12501,21 @@
         <v>14</v>
       </c>
       <c r="J278" t="s" s="0">
-        <v>771</v>
+        <v>809</v>
       </c>
       <c r="K278" t="s" s="0">
-        <v>772</v>
+        <v>810</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s" s="1">
-        <v>773</v>
+        <v>811</v>
       </c>
       <c r="B279" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C279" t="s" s="1">
-        <v>774</v>
+        <v>812</v>
       </c>
       <c r="D279" t="n" s="0">
         <v>1.0</v>
@@ -12413,21 +12536,21 @@
         <v>14</v>
       </c>
       <c r="J279" t="s" s="0">
-        <v>775</v>
+        <v>813</v>
       </c>
       <c r="K279" t="s" s="0">
-        <v>776</v>
+        <v>814</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s" s="1">
-        <v>777</v>
+        <v>815</v>
       </c>
       <c r="B280" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C280" t="s" s="1">
-        <v>778</v>
+        <v>816</v>
       </c>
       <c r="D280" t="n" s="0">
         <v>1.0</v>
@@ -12448,27 +12571,27 @@
         <v>14</v>
       </c>
       <c r="J280" t="s" s="0">
-        <v>779</v>
+        <v>817</v>
       </c>
       <c r="K280" t="s" s="0">
-        <v>780</v>
+        <v>818</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s" s="1">
-        <v>781</v>
+        <v>819</v>
       </c>
       <c r="B281" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C281" t="s" s="1">
-        <v>782</v>
+        <v>820</v>
       </c>
       <c r="D281" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E281" t="s" s="0">
-        <v>14</v>
+        <v>821</v>
       </c>
       <c r="F281" t="s" s="2">
         <v>14</v>
@@ -12483,27 +12606,27 @@
         <v>14</v>
       </c>
       <c r="J281" t="s" s="0">
-        <v>783</v>
+        <v>822</v>
       </c>
       <c r="K281" t="s" s="0">
-        <v>784</v>
+        <v>823</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s" s="1">
-        <v>785</v>
+        <v>824</v>
       </c>
       <c r="B282" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C282" t="s" s="1">
-        <v>786</v>
+        <v>825</v>
       </c>
       <c r="D282" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E282" t="s" s="0">
-        <v>14</v>
+        <v>826</v>
       </c>
       <c r="F282" t="s" s="2">
         <v>14</v>
@@ -12518,27 +12641,27 @@
         <v>14</v>
       </c>
       <c r="J282" t="s" s="0">
-        <v>787</v>
+        <v>827</v>
       </c>
       <c r="K282" t="s" s="0">
-        <v>788</v>
+        <v>828</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s" s="1">
-        <v>789</v>
+        <v>829</v>
       </c>
       <c r="B283" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C283" t="s" s="1">
-        <v>790</v>
+        <v>830</v>
       </c>
       <c r="D283" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E283" t="s" s="0">
-        <v>791</v>
+        <v>831</v>
       </c>
       <c r="F283" t="s" s="2">
         <v>14</v>
@@ -12553,21 +12676,21 @@
         <v>14</v>
       </c>
       <c r="J283" t="s" s="0">
-        <v>792</v>
+        <v>832</v>
       </c>
       <c r="K283" t="s" s="0">
-        <v>793</v>
+        <v>833</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s" s="1">
-        <v>794</v>
+        <v>834</v>
       </c>
       <c r="B284" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C284" t="s" s="1">
-        <v>795</v>
+        <v>835</v>
       </c>
       <c r="D284" t="n" s="0">
         <v>1.0</v>
@@ -12588,27 +12711,27 @@
         <v>14</v>
       </c>
       <c r="J284" t="s" s="0">
-        <v>796</v>
+        <v>836</v>
       </c>
       <c r="K284" t="s" s="0">
-        <v>797</v>
+        <v>837</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s" s="1">
-        <v>798</v>
+        <v>838</v>
       </c>
       <c r="B285" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C285" t="s" s="1">
-        <v>799</v>
+        <v>839</v>
       </c>
       <c r="D285" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E285" t="s" s="0">
-        <v>14</v>
+        <v>840</v>
       </c>
       <c r="F285" t="s" s="2">
         <v>14</v>
@@ -12623,21 +12746,21 @@
         <v>14</v>
       </c>
       <c r="J285" t="s" s="0">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="K285" t="s" s="0">
-        <v>801</v>
+        <v>842</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s" s="1">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="B286" t="s" s="0">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="C286" t="s" s="1">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="D286" t="n" s="0">
         <v>1.0</v>
@@ -12658,10 +12781,10 @@
         <v>14</v>
       </c>
       <c r="J286" t="s" s="0">
-        <v>804</v>
+        <v>845</v>
       </c>
       <c r="K286" t="s" s="0">
-        <v>805</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -13261,212 +13384,212 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>806</v>
+        <v>847</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>807</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>809</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>810</v>
+        <v>851</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>811</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>812</v>
+        <v>853</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>813</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>814</v>
+        <v>855</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>815</v>
+        <v>856</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>816</v>
+        <v>857</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>817</v>
+        <v>858</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>818</v>
+        <v>859</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>819</v>
+        <v>860</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>820</v>
+        <v>861</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>821</v>
+        <v>862</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>822</v>
+        <v>863</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>823</v>
+        <v>864</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>824</v>
+        <v>865</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>825</v>
+        <v>866</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>826</v>
+        <v>867</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>827</v>
+        <v>868</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>828</v>
+        <v>869</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>829</v>
+        <v>870</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>830</v>
+        <v>871</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>831</v>
+        <v>872</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>832</v>
+        <v>873</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>833</v>
+        <v>874</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>834</v>
+        <v>875</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>835</v>
+        <v>876</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>836</v>
+        <v>877</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>837</v>
+        <v>878</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>838</v>
+        <v>879</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>839</v>
+        <v>880</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>840</v>
+        <v>881</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>841</v>
+        <v>882</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>842</v>
+        <v>883</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>843</v>
+        <v>884</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>844</v>
+        <v>885</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>845</v>
+        <v>886</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>846</v>
+        <v>887</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>847</v>
+        <v>888</v>
       </c>
     </row>
   </sheetData>
